--- a/InputData/trans/ICtPSFfL/Incremental Cost to Produce Substitute Fuel for LCFS.xlsx
+++ b/InputData/trans/ICtPSFfL/Incremental Cost to Produce Substitute Fuel for LCFS.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10402"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\trans\ICtPSFfL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/trans/ICtPSFfL/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD536FA-1685-AB4A-B96C-92436A8DCE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13800"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="2" r:id="rId1"/>
@@ -28,10 +29,21 @@
     <definedName name="nonlignite_multiplier">#REF!</definedName>
     <definedName name="use_lifecycle_biofuel_EIs">[1]About!$A$61</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -172,7 +184,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -216,10 +228,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -243,7 +254,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="About"/>
@@ -574,113 +585,113 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B5" s="4">
         <v>2018</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
         <v>947817.12</v>
       </c>
       <c r="B24" t="s">
@@ -694,20 +705,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AK35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.5" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:37" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B2">
         <v>2015</v>
       </c>
@@ -817,7 +828,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -930,7 +941,7 @@
         <v>38.8994534841326</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1043,7 +1054,7 @@
         <v>47.526138928681398</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -1156,7 +1167,7 @@
         <v>36.031200708728697</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1269,7 +1280,7 @@
         <v>41.934834775512002</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1282,7 +1293,7 @@
       <c r="D7">
         <v>18.885450227945402</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7">
         <v>19.0133949371196</v>
       </c>
       <c r="F7">
@@ -1382,7 +1393,7 @@
         <v>36.031508112322399</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1495,12 +1506,12 @@
         <v>39.309585492238803</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -1613,7 +1624,7 @@
         <v>38.8994534841326</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -1726,12 +1737,12 @@
         <v>47.526138928681398</v>
       </c>
     </row>
-    <row r="13" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:37" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1880,7 +1891,7 @@
         <v>4.1041096075720387E-5</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -2029,7 +2040,7 @@
         <v>5.0142731045712066E-5</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -2178,7 +2189,7 @@
         <v>3.8014929197236589E-5</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -2327,7 +2338,7 @@
         <v>4.4243592873182117E-5</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -2476,7 +2487,7 @@
         <v>3.8015253525197351E-5</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -2625,7 +2636,7 @@
         <v>4.1473808251362669E-5</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -2774,7 +2785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -2923,7 +2934,7 @@
         <v>4.1041096075720387E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>1</v>
       </c>
@@ -3072,12 +3083,12 @@
         <v>5.0142731045712066E-5</v>
       </c>
     </row>
-    <row r="24" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:37" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -3085,7 +3096,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -3093,7 +3104,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -3101,7 +3112,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -3109,12 +3120,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:37" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>2015</v>
       </c>
@@ -3224,7 +3235,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -3337,7 +3348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -3450,7 +3461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>13</v>
       </c>
@@ -3599,7 +3610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>14</v>
       </c>
@@ -3754,18 +3765,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BE11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
+    <col min="1" max="1" width="23.83203125" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -3877,8 +3888,68 @@
       <c r="AK1">
         <v>2050</v>
       </c>
+      <c r="AL1">
+        <v>2051</v>
+      </c>
+      <c r="AM1">
+        <v>2052</v>
+      </c>
+      <c r="AN1">
+        <v>2053</v>
+      </c>
+      <c r="AO1">
+        <v>2054</v>
+      </c>
+      <c r="AP1">
+        <v>2055</v>
+      </c>
+      <c r="AQ1">
+        <v>2056</v>
+      </c>
+      <c r="AR1">
+        <v>2057</v>
+      </c>
+      <c r="AS1">
+        <v>2058</v>
+      </c>
+      <c r="AT1">
+        <v>2059</v>
+      </c>
+      <c r="AU1">
+        <v>2060</v>
+      </c>
+      <c r="AV1">
+        <v>2061</v>
+      </c>
+      <c r="AW1">
+        <v>2062</v>
+      </c>
+      <c r="AX1">
+        <v>2063</v>
+      </c>
+      <c r="AY1">
+        <v>2064</v>
+      </c>
+      <c r="AZ1">
+        <v>2065</v>
+      </c>
+      <c r="BA1">
+        <v>2066</v>
+      </c>
+      <c r="BB1">
+        <v>2067</v>
+      </c>
+      <c r="BC1">
+        <v>2068</v>
+      </c>
+      <c r="BD1">
+        <v>2069</v>
+      </c>
+      <c r="BE1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -4026,8 +4097,88 @@
         <f>Calcs!AK32</f>
         <v>0</v>
       </c>
+      <c r="AL2">
+        <f>AK2</f>
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" ref="AM2:BE11" si="0">AL2</f>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -4175,8 +4326,88 @@
         <f>Calcs!AK33</f>
         <v>0</v>
       </c>
+      <c r="AL3">
+        <f t="shared" ref="AL3:BA11" si="1">AK3</f>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -4324,8 +4555,88 @@
         <f>0</f>
         <v>0</v>
       </c>
+      <c r="AL4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -4473,8 +4784,88 @@
         <f>0</f>
         <v>0</v>
       </c>
+      <c r="AL5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -4622,8 +5013,88 @@
         <f>Calcs!AK34</f>
         <v>0</v>
       </c>
+      <c r="AL6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -4771,8 +5242,88 @@
         <f>MAX(Calcs!AK35,0)</f>
         <v>0</v>
       </c>
+      <c r="AL7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -4920,8 +5471,88 @@
         <f>0</f>
         <v>0</v>
       </c>
+      <c r="AL8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -5069,8 +5700,88 @@
         <f>0</f>
         <v>0</v>
       </c>
+      <c r="AL9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -5218,8 +5929,88 @@
         <f>0</f>
         <v>0</v>
       </c>
+      <c r="AL10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -5365,6 +6156,86 @@
       </c>
       <c r="AK11">
         <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
